--- a/aggregate/raw_local_search/aggregate_local_search_numeric.xlsx
+++ b/aggregate/raw_local_search/aggregate_local_search_numeric.xlsx
@@ -27,9 +27,54 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="42">
   <si>
     <t>model</t>
+  </si>
+  <si>
+    <t>clusters</t>
+  </si>
+  <si>
+    <t>rounds_mean</t>
+  </si>
+  <si>
+    <t>rounds_std</t>
+  </si>
+  <si>
+    <t>trans_mean</t>
+  </si>
+  <si>
+    <t>trans_std</t>
+  </si>
+  <si>
+    <t>batch_mean</t>
+  </si>
+  <si>
+    <t>batch_std</t>
+  </si>
+  <si>
+    <t>total_batch_mean</t>
+  </si>
+  <si>
+    <t>total_batch_std</t>
+  </si>
+  <si>
+    <t>minibatch_rounds_mean</t>
+  </si>
+  <si>
+    <t>minibatch_rounds_std</t>
+  </si>
+  <si>
+    <t>epsilon_mean</t>
+  </si>
+  <si>
+    <t>epsilon_std</t>
+  </si>
+  <si>
+    <t>iteration_mean</t>
+  </si>
+  <si>
+    <t>iteration_std</t>
   </si>
   <si>
     <t>ARI_mean</t>
@@ -121,14 +166,7 @@
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="0.000_ "/>
   </numFmts>
-  <fonts count="21">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -599,154 +637,157 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1095,16 +1136,25 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:U7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="6"/>
+  <dimension ref="A1:AJ8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="7"/>
   <cols>
-    <col min="1" max="1" width="33.8888888888889" customWidth="1"/>
-    <col min="2" max="17" width="12.8888888888889"/>
-    <col min="18" max="18" width="13"/>
-    <col min="19" max="21" width="12.8888888888889"/>
+    <col min="1" max="1" width="22.6666666666667" customWidth="1"/>
+    <col min="2" max="2" width="12.8888888888889" hidden="1" customWidth="1"/>
+    <col min="3" max="4" width="9" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="12.8888888888889" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="9" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="9.66666666666667" hidden="1" customWidth="1"/>
+    <col min="8" max="12" width="9" hidden="1" customWidth="1"/>
+    <col min="13" max="13" width="12.8888888888889" hidden="1" customWidth="1"/>
+    <col min="14" max="15" width="9" hidden="1" customWidth="1"/>
+    <col min="16" max="16" width="12.8888888888889" hidden="1" customWidth="1"/>
+    <col min="17" max="32" width="12.8888888888889"/>
+    <col min="33" max="33" width="13"/>
+    <col min="34" max="36" width="12.8888888888889"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21">
+    <row r="1" spans="1:36">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1168,396 +1218,749 @@
       <c r="U1" s="1" t="s">
         <v>20</v>
       </c>
+      <c r="V1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AD1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AE1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="AF1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="AG1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="AH1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AI1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="AJ1" s="1" t="s">
+        <v>35</v>
+      </c>
     </row>
-    <row r="2" spans="1:21">
+    <row r="2" spans="1:36">
       <c r="A2" s="1" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="B2" s="1">
+        <v>35.1818181818182</v>
+      </c>
+      <c r="C2" s="1">
+        <v>60</v>
+      </c>
+      <c r="D2" s="1">
+        <v>0</v>
+      </c>
+      <c r="E2" s="1">
+        <v>43.1818181818182</v>
+      </c>
+      <c r="F2" s="1">
+        <v>0</v>
+      </c>
+      <c r="G2" s="1">
+        <v>880</v>
+      </c>
+      <c r="H2" s="1">
+        <v>0</v>
+      </c>
+      <c r="I2" s="1">
+        <v>15</v>
+      </c>
+      <c r="J2" s="1">
+        <v>0</v>
+      </c>
+      <c r="K2" s="1">
+        <v>30</v>
+      </c>
+      <c r="L2" s="1">
+        <v>0</v>
+      </c>
+      <c r="M2" s="1">
+        <v>0.516206951136723</v>
+      </c>
+      <c r="N2" s="1">
+        <v>0</v>
+      </c>
+      <c r="O2" s="1">
+        <v>14.5</v>
+      </c>
+      <c r="P2" s="1">
+        <v>8.8034084308295</v>
+      </c>
+      <c r="Q2" s="1">
         <v>0.473568313050065</v>
       </c>
-      <c r="C2" s="1">
+      <c r="R2" s="1">
         <v>0.0330921930914993</v>
       </c>
-      <c r="D2" s="1">
+      <c r="S2" s="1">
         <v>0.63569830021543</v>
       </c>
-      <c r="E2" s="1">
+      <c r="T2" s="1">
         <v>0.0153207732418373</v>
       </c>
-      <c r="F2" s="1">
+      <c r="U2" s="1">
         <v>3.27355400475846</v>
       </c>
-      <c r="G2" s="1">
+      <c r="V2" s="1">
         <v>0.0929784448611127</v>
       </c>
-      <c r="H2" s="1">
+      <c r="W2" s="1">
         <v>461.549493535236</v>
       </c>
-      <c r="I2" s="1">
+      <c r="X2" s="1">
         <v>12.2669959935394</v>
       </c>
-      <c r="J2" s="1">
+      <c r="Y2" s="1">
         <v>0.604532796128626</v>
       </c>
-      <c r="K2" s="1">
+      <c r="Z2" s="1">
         <v>0.0394534033935735</v>
       </c>
-      <c r="L2" s="1">
+      <c r="AA2" s="1">
         <v>0.613952420270681</v>
       </c>
-      <c r="M2" s="1">
+      <c r="AB2" s="1">
         <v>0.0423042482172551</v>
       </c>
-      <c r="N2" s="1">
+      <c r="AC2" s="1">
         <v>0.604532796128626</v>
       </c>
-      <c r="O2" s="1">
+      <c r="AD2" s="1">
         <v>0.0394534033935735</v>
       </c>
-      <c r="P2" s="1">
+      <c r="AE2" s="1">
         <v>0.684435332102612</v>
       </c>
-      <c r="Q2" s="1">
+      <c r="AF2" s="1">
         <v>0.0407836512228667</v>
       </c>
-      <c r="R2" s="1">
+      <c r="AG2" s="1">
         <v>15527.1882233591</v>
       </c>
-      <c r="S2" s="1">
+      <c r="AH2" s="1">
         <v>49.3740270932161</v>
       </c>
-      <c r="T2" s="1">
-        <v>1.37974004384243</v>
-      </c>
-      <c r="U2" s="1">
-        <v>0.279047601600285</v>
+      <c r="AI2" s="1">
+        <v>1.51358215086388</v>
+      </c>
+      <c r="AJ2" s="1">
+        <v>0.173904401182461</v>
       </c>
     </row>
-    <row r="3" spans="1:21">
+    <row r="3" spans="1:36">
       <c r="A3" s="1" t="s">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="B3" s="1">
+        <v>35.1818181818182</v>
+      </c>
+      <c r="C3" s="1">
+        <v>60</v>
+      </c>
+      <c r="D3" s="1">
+        <v>0</v>
+      </c>
+      <c r="E3" s="1">
+        <v>43.1818181818182</v>
+      </c>
+      <c r="F3" s="1">
+        <v>0</v>
+      </c>
+      <c r="G3" s="1">
+        <v>880</v>
+      </c>
+      <c r="H3" s="1">
+        <v>0</v>
+      </c>
+      <c r="I3" s="1">
+        <v>15</v>
+      </c>
+      <c r="J3" s="1">
+        <v>0</v>
+      </c>
+      <c r="K3" s="1">
+        <v>30</v>
+      </c>
+      <c r="L3" s="1">
+        <v>0</v>
+      </c>
+      <c r="M3" s="1">
+        <v>0.516206951136723</v>
+      </c>
+      <c r="N3" s="1">
+        <v>0</v>
+      </c>
+      <c r="O3" s="1">
+        <v>14.5</v>
+      </c>
+      <c r="P3" s="1">
+        <v>8.8034084308295</v>
+      </c>
+      <c r="Q3" s="1">
         <v>0.488034575913831</v>
       </c>
-      <c r="C3" s="1">
+      <c r="R3" s="1">
         <v>0.0326100921363776</v>
       </c>
-      <c r="D3" s="1">
+      <c r="S3" s="1">
         <v>0.647343075820886</v>
       </c>
-      <c r="E3" s="1">
+      <c r="T3" s="1">
         <v>0.0165567708793915</v>
       </c>
-      <c r="F3" s="1">
+      <c r="U3" s="1">
         <v>3.32332331853802</v>
       </c>
-      <c r="G3" s="1">
+      <c r="V3" s="1">
         <v>0.106089437964309</v>
       </c>
-      <c r="H3" s="1">
+      <c r="W3" s="1">
         <v>446.51840908488</v>
       </c>
-      <c r="I3" s="1">
+      <c r="X3" s="1">
         <v>11.1937847366069</v>
       </c>
-      <c r="J3" s="1">
+      <c r="Y3" s="1">
         <v>0.611186527962527</v>
       </c>
-      <c r="K3" s="1">
+      <c r="Z3" s="1">
         <v>0.0357701648142329</v>
       </c>
-      <c r="L3" s="1">
+      <c r="AA3" s="1">
         <v>0.618981732783829</v>
       </c>
-      <c r="M3" s="1">
+      <c r="AB3" s="1">
         <v>0.0386317746287192</v>
       </c>
-      <c r="N3" s="1">
+      <c r="AC3" s="1">
         <v>0.611186527962527</v>
       </c>
-      <c r="O3" s="1">
+      <c r="AD3" s="1">
         <v>0.0357701648142329</v>
       </c>
-      <c r="P3" s="1">
+      <c r="AE3" s="1">
         <v>0.684059817753821</v>
       </c>
-      <c r="Q3" s="1">
+      <c r="AF3" s="1">
         <v>0.0380338355598653</v>
       </c>
-      <c r="R3" s="1">
+      <c r="AG3" s="1">
         <v>15789.9633934715</v>
       </c>
-      <c r="S3" s="1">
+      <c r="AH3" s="1">
         <v>46.8224451831279</v>
       </c>
-      <c r="T3" s="1">
-        <v>1.55176832748182</v>
-      </c>
-      <c r="U3" s="1">
-        <v>0.163210063650829</v>
+      <c r="AI3" s="1">
+        <v>1.51348014383605</v>
+      </c>
+      <c r="AJ3" s="1">
+        <v>0.154464196771965</v>
       </c>
     </row>
-    <row r="4" spans="1:21">
+    <row r="4" spans="1:36">
       <c r="A4" s="1" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="B4" s="1">
+        <v>35.1818181818182</v>
+      </c>
+      <c r="C4" s="1">
+        <v>60</v>
+      </c>
+      <c r="D4" s="1">
+        <v>0</v>
+      </c>
+      <c r="E4" s="1">
+        <v>43.1818181818182</v>
+      </c>
+      <c r="F4" s="1">
+        <v>0</v>
+      </c>
+      <c r="G4" s="1">
+        <v>880</v>
+      </c>
+      <c r="H4" s="1">
+        <v>0</v>
+      </c>
+      <c r="I4" s="1">
+        <v>15</v>
+      </c>
+      <c r="J4" s="1">
+        <v>0</v>
+      </c>
+      <c r="K4" s="1">
+        <v>30</v>
+      </c>
+      <c r="L4" s="1">
+        <v>0</v>
+      </c>
+      <c r="M4" s="1">
+        <v>0.516206951136723</v>
+      </c>
+      <c r="N4" s="1">
+        <v>0</v>
+      </c>
+      <c r="O4" s="1">
+        <v>14.5</v>
+      </c>
+      <c r="P4" s="1">
+        <v>8.8034084308295</v>
+      </c>
+      <c r="Q4" s="1">
         <v>0.495547847566887</v>
       </c>
-      <c r="C4" s="1">
+      <c r="R4" s="1">
         <v>0.0362031611729723</v>
       </c>
-      <c r="D4" s="1">
+      <c r="S4" s="1">
         <v>0.658759923036448</v>
       </c>
-      <c r="E4" s="1">
+      <c r="T4" s="1">
         <v>0.0171632077462643</v>
       </c>
-      <c r="F4" s="1">
+      <c r="U4" s="1">
         <v>3.28107322082918</v>
       </c>
-      <c r="G4" s="1">
+      <c r="V4" s="1">
         <v>0.084778162822768</v>
       </c>
-      <c r="H4" s="1">
+      <c r="W4" s="1">
         <v>425.440261975572</v>
       </c>
-      <c r="I4" s="1">
+      <c r="X4" s="1">
         <v>8.88894312266922</v>
       </c>
-      <c r="J4" s="1">
+      <c r="Y4" s="1">
         <v>0.61588675157525</v>
       </c>
-      <c r="K4" s="1">
+      <c r="Z4" s="1">
         <v>0.0393335852916856</v>
       </c>
-      <c r="L4" s="1">
+      <c r="AA4" s="1">
         <v>0.623822698777201</v>
       </c>
-      <c r="M4" s="1">
+      <c r="AB4" s="1">
         <v>0.04237706785423</v>
       </c>
-      <c r="N4" s="1">
+      <c r="AC4" s="1">
         <v>0.61588675157525</v>
       </c>
-      <c r="O4" s="1">
+      <c r="AD4" s="1">
         <v>0.0393335852916856</v>
       </c>
-      <c r="P4" s="1">
+      <c r="AE4" s="1">
         <v>0.694766652743775</v>
       </c>
-      <c r="Q4" s="1">
+      <c r="AF4" s="1">
         <v>0.0409585066849247</v>
       </c>
-      <c r="R4" s="1">
+      <c r="AG4" s="1">
         <v>15917.4837077748</v>
       </c>
-      <c r="S4" s="1">
+      <c r="AH4" s="1">
         <v>44.6170245783706</v>
       </c>
-      <c r="T4" s="1">
-        <v>2.7021624174985</v>
-      </c>
-      <c r="U4" s="1">
-        <v>0.364527484639452</v>
+      <c r="AI4" s="1">
+        <v>2.80864450570309</v>
+      </c>
+      <c r="AJ4" s="1">
+        <v>0.314677665392756</v>
       </c>
     </row>
-    <row r="5" spans="1:21">
+    <row r="5" spans="1:36">
       <c r="A5" s="1" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="B5" s="1">
+        <v>35.1818181818182</v>
+      </c>
+      <c r="C5" s="1">
+        <v>60</v>
+      </c>
+      <c r="D5" s="1">
+        <v>0</v>
+      </c>
+      <c r="E5" s="1">
+        <v>43.1818181818182</v>
+      </c>
+      <c r="F5" s="1">
+        <v>0</v>
+      </c>
+      <c r="G5" s="1">
+        <v>880</v>
+      </c>
+      <c r="H5" s="1">
+        <v>0</v>
+      </c>
+      <c r="I5" s="1">
+        <v>15</v>
+      </c>
+      <c r="J5" s="1">
+        <v>0</v>
+      </c>
+      <c r="K5" s="1">
+        <v>30</v>
+      </c>
+      <c r="L5" s="1">
+        <v>0</v>
+      </c>
+      <c r="M5" s="1">
+        <v>0.516206951136723</v>
+      </c>
+      <c r="N5" s="1">
+        <v>0</v>
+      </c>
+      <c r="O5" s="1">
+        <v>14.5</v>
+      </c>
+      <c r="P5" s="1">
+        <v>8.8034084308295</v>
+      </c>
+      <c r="Q5" s="1">
         <v>0.52165843528728</v>
       </c>
-      <c r="C5" s="1">
+      <c r="R5" s="1">
         <v>0.0439037944335897</v>
       </c>
-      <c r="D5" s="1">
+      <c r="S5" s="1">
         <v>0.67992131943443</v>
       </c>
-      <c r="E5" s="1">
+      <c r="T5" s="1">
         <v>0.0201048202713056</v>
       </c>
-      <c r="F5" s="1">
+      <c r="U5" s="1">
         <v>3.51151370115819</v>
       </c>
-      <c r="G5" s="1">
+      <c r="V5" s="1">
         <v>0.104995431161596</v>
       </c>
-      <c r="H5" s="1">
+      <c r="W5" s="1">
         <v>446.433741532925</v>
       </c>
-      <c r="I5" s="1">
+      <c r="X5" s="1">
         <v>14.8483115244355</v>
       </c>
-      <c r="J5" s="1">
+      <c r="Y5" s="1">
         <v>0.632799439112831</v>
       </c>
-      <c r="K5" s="1">
+      <c r="Z5" s="1">
         <v>0.0486514231524696</v>
       </c>
-      <c r="L5" s="1">
+      <c r="AA5" s="1">
         <v>0.638270187369299</v>
       </c>
-      <c r="M5" s="1">
+      <c r="AB5" s="1">
         <v>0.0533531517306848</v>
       </c>
-      <c r="N5" s="1">
+      <c r="AC5" s="1">
         <v>0.632799439112831</v>
       </c>
-      <c r="O5" s="1">
+      <c r="AD5" s="1">
         <v>0.0486514231524696</v>
       </c>
-      <c r="P5" s="1">
+      <c r="AE5" s="1">
         <v>0.700915179167673</v>
       </c>
-      <c r="Q5" s="1">
+      <c r="AF5" s="1">
         <v>0.0529371559476419</v>
       </c>
-      <c r="R5" s="1">
+      <c r="AG5" s="1">
         <v>4462.63461960301</v>
       </c>
-      <c r="S5" s="1">
+      <c r="AH5" s="1">
         <v>16.7575286704613</v>
       </c>
-      <c r="T5" s="1">
-        <v>2.63635911797032</v>
-      </c>
-      <c r="U5" s="1">
-        <v>0.345510275014465</v>
+      <c r="AI5" s="1">
+        <v>2.8735463958798</v>
+      </c>
+      <c r="AJ5" s="1">
+        <v>0.324608551102211</v>
       </c>
     </row>
-    <row r="6" spans="1:21">
+    <row r="6" spans="1:36">
       <c r="A6" s="1" t="s">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="B6" s="1">
+        <v>35.1818181818182</v>
+      </c>
+      <c r="C6" s="1">
+        <v>60</v>
+      </c>
+      <c r="D6" s="1">
+        <v>0</v>
+      </c>
+      <c r="E6" s="1">
+        <v>43.1818181818182</v>
+      </c>
+      <c r="F6" s="1">
+        <v>0</v>
+      </c>
+      <c r="G6" s="1">
+        <v>880</v>
+      </c>
+      <c r="H6" s="1">
+        <v>0</v>
+      </c>
+      <c r="I6" s="1">
+        <v>15</v>
+      </c>
+      <c r="J6" s="1">
+        <v>0</v>
+      </c>
+      <c r="K6" s="1">
+        <v>30</v>
+      </c>
+      <c r="L6" s="1">
+        <v>0</v>
+      </c>
+      <c r="M6" s="1">
+        <v>0.516206951136723</v>
+      </c>
+      <c r="N6" s="1">
+        <v>0</v>
+      </c>
+      <c r="O6" s="1">
+        <v>14.5</v>
+      </c>
+      <c r="P6" s="1">
+        <v>8.8034084308295</v>
+      </c>
+      <c r="Q6" s="1">
         <v>0.457896366197763</v>
       </c>
-      <c r="C6" s="1">
+      <c r="R6" s="1">
         <v>0.0381848549186297</v>
       </c>
-      <c r="D6" s="1">
+      <c r="S6" s="1">
         <v>0.62525307650291</v>
       </c>
-      <c r="E6" s="1">
+      <c r="T6" s="1">
         <v>0.0206299951071261</v>
       </c>
-      <c r="F6" s="1">
+      <c r="U6" s="1">
         <v>3.49089748666789</v>
       </c>
-      <c r="G6" s="1">
+      <c r="V6" s="1">
         <v>0.118899916950087</v>
       </c>
-      <c r="H6" s="1">
+      <c r="W6" s="1">
         <v>516.675809408243</v>
       </c>
-      <c r="I6" s="1">
+      <c r="X6" s="1">
         <v>9.80239327174251</v>
       </c>
-      <c r="J6" s="1">
+      <c r="Y6" s="1">
         <v>0.596143469699791</v>
       </c>
-      <c r="K6" s="1">
+      <c r="Z6" s="1">
         <v>0.0422331731007151</v>
       </c>
-      <c r="L6" s="1">
+      <c r="AA6" s="1">
         <v>0.610502258200248</v>
       </c>
-      <c r="M6" s="1">
+      <c r="AB6" s="1">
         <v>0.0457389747476395</v>
       </c>
-      <c r="N6" s="1">
+      <c r="AC6" s="1">
         <v>0.596143469699791</v>
       </c>
-      <c r="O6" s="1">
+      <c r="AD6" s="1">
         <v>0.0422331731007151</v>
       </c>
-      <c r="P6" s="1">
+      <c r="AE6" s="1">
         <v>0.688836382695337</v>
       </c>
-      <c r="Q6" s="1">
+      <c r="AF6" s="1">
         <v>0.0456415704046133</v>
       </c>
-      <c r="R6" s="1">
+      <c r="AG6" s="1">
         <v>10256.0473921342</v>
       </c>
-      <c r="S6" s="1">
+      <c r="AH6" s="1">
         <v>24.2071677853238</v>
       </c>
-      <c r="T6" s="1">
-        <v>2.87369475581429</v>
-      </c>
-      <c r="U6" s="1">
-        <v>0.313987266918428</v>
+      <c r="AI6" s="1">
+        <v>3.02785122394562</v>
+      </c>
+      <c r="AJ6" s="1">
+        <v>0.445337492514397</v>
       </c>
     </row>
-    <row r="7" spans="1:21">
+    <row r="7" spans="1:36">
       <c r="A7" s="1" t="s">
-        <v>26</v>
+        <v>41</v>
       </c>
       <c r="B7" s="1">
+        <v>35.1818181818182</v>
+      </c>
+      <c r="C7" s="1">
+        <v>60</v>
+      </c>
+      <c r="D7" s="1">
+        <v>0</v>
+      </c>
+      <c r="E7" s="1">
+        <v>43.1818181818182</v>
+      </c>
+      <c r="F7" s="1">
+        <v>0</v>
+      </c>
+      <c r="G7" s="1">
+        <v>880</v>
+      </c>
+      <c r="H7" s="1">
+        <v>0</v>
+      </c>
+      <c r="I7" s="1">
+        <v>15</v>
+      </c>
+      <c r="J7" s="1">
+        <v>0</v>
+      </c>
+      <c r="K7" s="1">
+        <v>30</v>
+      </c>
+      <c r="L7" s="1">
+        <v>0</v>
+      </c>
+      <c r="M7" s="1">
+        <v>0.516206951136723</v>
+      </c>
+      <c r="N7" s="1">
+        <v>0</v>
+      </c>
+      <c r="O7" s="1">
+        <v>14.5</v>
+      </c>
+      <c r="P7" s="1">
+        <v>8.8034084308295</v>
+      </c>
+      <c r="Q7" s="1">
         <v>0.338446729141413</v>
       </c>
-      <c r="C7" s="1">
+      <c r="R7" s="1">
         <v>0.0204606162757899</v>
       </c>
-      <c r="D7" s="1">
+      <c r="S7" s="1">
         <v>0.517918009154525</v>
       </c>
-      <c r="E7" s="1">
+      <c r="T7" s="1">
         <v>0.0153702738547358</v>
       </c>
-      <c r="F7" s="1">
+      <c r="U7" s="1">
         <v>3.06579139884464</v>
       </c>
-      <c r="G7" s="1">
+      <c r="V7" s="1">
         <v>0.099358397413221</v>
       </c>
-      <c r="H7" s="1">
+      <c r="W7" s="1">
         <v>462.084581509486</v>
       </c>
-      <c r="I7" s="1">
+      <c r="X7" s="1">
         <v>9.8283722381845</v>
       </c>
-      <c r="J7" s="1">
+      <c r="Y7" s="1">
         <v>0.511172462949219</v>
       </c>
-      <c r="K7" s="1">
+      <c r="Z7" s="1">
         <v>0.0250283629054177</v>
       </c>
-      <c r="L7" s="1">
+      <c r="AA7" s="1">
         <v>0.516583087109385</v>
       </c>
-      <c r="M7" s="1">
+      <c r="AB7" s="1">
         <v>0.0287446525885796</v>
       </c>
-      <c r="N7" s="1">
+      <c r="AC7" s="1">
         <v>0.511172462949219</v>
       </c>
-      <c r="O7" s="1">
+      <c r="AD7" s="1">
         <v>0.0250283629054177</v>
       </c>
-      <c r="P7" s="1">
+      <c r="AE7" s="1">
         <v>0.590740001538912</v>
       </c>
-      <c r="Q7" s="1">
+      <c r="AF7" s="1">
         <v>0.0380418487337773</v>
       </c>
-      <c r="R7" s="1">
+      <c r="AG7" s="1">
         <v>268643.250488836</v>
       </c>
-      <c r="S7" s="1">
+      <c r="AH7" s="1">
         <v>889.675658330147</v>
       </c>
-      <c r="T7" s="1">
-        <v>1.42186646461487</v>
-      </c>
-      <c r="U7" s="1">
-        <v>0.164096019777988</v>
-      </c>
+      <c r="AI7" s="1">
+        <v>1.48168746991591</v>
+      </c>
+      <c r="AJ7" s="1">
+        <v>0.178978279802395</v>
+      </c>
+    </row>
+    <row r="8" spans="1:36">
+      <c r="A8" s="2"/>
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+      <c r="F8" s="2"/>
+      <c r="G8" s="2"/>
+      <c r="H8" s="2"/>
+      <c r="I8" s="2"/>
+      <c r="J8" s="2"/>
+      <c r="K8" s="2"/>
+      <c r="L8" s="2"/>
+      <c r="M8" s="2"/>
+      <c r="N8" s="2"/>
+      <c r="O8" s="2"/>
+      <c r="P8" s="2"/>
+      <c r="Q8" s="2"/>
+      <c r="R8" s="2"/>
+      <c r="S8" s="2"/>
+      <c r="T8" s="2"/>
+      <c r="U8" s="2"/>
+      <c r="V8" s="2"/>
+      <c r="W8" s="2"/>
+      <c r="X8" s="2"/>
+      <c r="Y8" s="2"/>
+      <c r="Z8" s="2"/>
+      <c r="AA8" s="2"/>
+      <c r="AB8" s="2"/>
+      <c r="AC8" s="2"/>
+      <c r="AD8" s="2"/>
+      <c r="AE8" s="2"/>
+      <c r="AF8" s="2"/>
+      <c r="AG8" s="2"/>
+      <c r="AH8" s="2"/>
+      <c r="AI8" s="2"/>
+      <c r="AJ8" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
